--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB298"/>
+  <dimension ref="A1:AB299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26949,6 +26949,96 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="C299" t="n">
+        <v>394.05</v>
+      </c>
+      <c r="D299" t="n">
+        <v>450.35</v>
+      </c>
+      <c r="E299" t="n">
+        <v>469.26</v>
+      </c>
+      <c r="F299" t="n">
+        <v>469.3</v>
+      </c>
+      <c r="G299" t="n">
+        <v>451.29</v>
+      </c>
+      <c r="H299" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="I299" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="J299" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="K299" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="L299" t="n">
+        <v>391.51</v>
+      </c>
+      <c r="M299" t="n">
+        <v>409.09</v>
+      </c>
+      <c r="N299" t="n">
+        <v>429.92</v>
+      </c>
+      <c r="O299" t="n">
+        <v>435.69</v>
+      </c>
+      <c r="P299" t="n">
+        <v>432.95</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>442.4</v>
+      </c>
+      <c r="R299" t="n">
+        <v>451.25</v>
+      </c>
+      <c r="S299" t="n">
+        <v>454.64</v>
+      </c>
+      <c r="T299" t="n">
+        <v>434.69</v>
+      </c>
+      <c r="U299" t="n">
+        <v>434.52</v>
+      </c>
+      <c r="V299" t="n">
+        <v>428.54</v>
+      </c>
+      <c r="W299" t="n">
+        <v>417.1</v>
+      </c>
+      <c r="X299" t="n">
+        <v>409.49</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>400.85</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>394.21</v>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26960,7 +27050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30043,6 +30133,16 @@
       </c>
       <c r="B308" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -30211,28 +30311,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.446125731053353</v>
+        <v>-1.527918178974103</v>
       </c>
       <c r="J2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K2" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02558242453600024</v>
+        <v>0.02844476321276901</v>
       </c>
       <c r="M2" t="n">
-        <v>57.09823110115454</v>
+        <v>57.42141222590541</v>
       </c>
       <c r="N2" t="n">
-        <v>4533.723886173388</v>
+        <v>4560.934970261533</v>
       </c>
       <c r="O2" t="n">
-        <v>67.33293314696299</v>
+        <v>67.53469456702631</v>
       </c>
       <c r="P2" t="n">
-        <v>507.1241210401299</v>
+        <v>507.9632753422042</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30289,28 +30389,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.687935197251909</v>
+        <v>-1.743762205148819</v>
       </c>
       <c r="J3" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03151679026536569</v>
+        <v>0.03371220069368763</v>
       </c>
       <c r="M3" t="n">
-        <v>55.63952178056842</v>
+        <v>55.80810002341784</v>
       </c>
       <c r="N3" t="n">
-        <v>4571.328401362174</v>
+        <v>4573.150448628172</v>
       </c>
       <c r="O3" t="n">
-        <v>67.61159960659246</v>
+        <v>67.62507263307133</v>
       </c>
       <c r="P3" t="n">
-        <v>510.7766163624184</v>
+        <v>511.38897762953</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30367,28 +30467,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.039516938469886</v>
+        <v>-1.055123674821883</v>
       </c>
       <c r="J4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0131029996770633</v>
+        <v>0.0136039418693823</v>
       </c>
       <c r="M4" t="n">
-        <v>54.36681962794761</v>
+        <v>54.2703127277707</v>
       </c>
       <c r="N4" t="n">
-        <v>4507.724316595734</v>
+        <v>4492.726323870455</v>
       </c>
       <c r="O4" t="n">
-        <v>67.13958829629307</v>
+        <v>67.02780261854372</v>
       </c>
       <c r="P4" t="n">
-        <v>498.9670415036695</v>
+        <v>499.1307783393051</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30445,28 +30545,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2256733557548926</v>
+        <v>-0.2336187801418805</v>
       </c>
       <c r="J5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007605681100241179</v>
+        <v>0.000821799436742543</v>
       </c>
       <c r="M5" t="n">
-        <v>49.80425966793968</v>
+        <v>49.66787049812806</v>
       </c>
       <c r="N5" t="n">
-        <v>3780.610598814837</v>
+        <v>3766.82256709818</v>
       </c>
       <c r="O5" t="n">
-        <v>61.48667009047438</v>
+        <v>61.37444555430362</v>
       </c>
       <c r="P5" t="n">
-        <v>485.9899925008736</v>
+        <v>486.0731429013834</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30523,28 +30623,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6358335835762214</v>
+        <v>0.6270265561378146</v>
       </c>
       <c r="J6" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006796296789401857</v>
+        <v>0.006662135657311663</v>
       </c>
       <c r="M6" t="n">
-        <v>45.29648071716814</v>
+        <v>45.19905112833863</v>
       </c>
       <c r="N6" t="n">
-        <v>3249.767294694354</v>
+        <v>3238.978421647166</v>
       </c>
       <c r="O6" t="n">
-        <v>57.00673025787705</v>
+        <v>56.91202352444662</v>
       </c>
       <c r="P6" t="n">
-        <v>464.7558634277307</v>
+        <v>464.8492433489508</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30601,28 +30701,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.130409208312856</v>
+        <v>1.104245449031509</v>
       </c>
       <c r="J7" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02360821127494028</v>
+        <v>0.02269062101590613</v>
       </c>
       <c r="M7" t="n">
-        <v>41.30323931872518</v>
+        <v>41.27029041887531</v>
       </c>
       <c r="N7" t="n">
-        <v>2865.863663740479</v>
+        <v>2860.580409491923</v>
       </c>
       <c r="O7" t="n">
-        <v>53.53376190536659</v>
+        <v>53.48439407427107</v>
       </c>
       <c r="P7" t="n">
-        <v>458.0093660772992</v>
+        <v>458.2907058572819</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30679,28 +30779,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.083200395686793</v>
+        <v>1.046704010650263</v>
       </c>
       <c r="J8" t="n">
+        <v>298</v>
+      </c>
+      <c r="K8" t="n">
         <v>297</v>
       </c>
-      <c r="K8" t="n">
-        <v>296</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03744134474954774</v>
+        <v>0.03511736339277849</v>
       </c>
       <c r="M8" t="n">
-        <v>32.66811577204692</v>
+        <v>32.71160339197372</v>
       </c>
       <c r="N8" t="n">
-        <v>1654.542634545359</v>
+        <v>1658.396812900188</v>
       </c>
       <c r="O8" t="n">
-        <v>40.67606955625579</v>
+        <v>40.72341848249221</v>
       </c>
       <c r="P8" t="n">
-        <v>445.8326112363686</v>
+        <v>446.2198658358234</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30757,28 +30857,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4886959637302933</v>
+        <v>0.4462728158770705</v>
       </c>
       <c r="J9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K9" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01358888333828567</v>
+        <v>0.01129561773799326</v>
       </c>
       <c r="M9" t="n">
-        <v>25.20953757292626</v>
+        <v>25.29876165185888</v>
       </c>
       <c r="N9" t="n">
-        <v>943.0309530975144</v>
+        <v>952.4313939046058</v>
       </c>
       <c r="O9" t="n">
-        <v>30.70880904720199</v>
+        <v>30.86148722768567</v>
       </c>
       <c r="P9" t="n">
-        <v>434.1944121910454</v>
+        <v>434.6479604723853</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30835,28 +30935,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3628957852667103</v>
+        <v>0.3186638855082527</v>
       </c>
       <c r="J10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K10" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0148047845402286</v>
+        <v>0.01121986745198522</v>
       </c>
       <c r="M10" t="n">
-        <v>18.40247938906513</v>
+        <v>18.58189505321621</v>
       </c>
       <c r="N10" t="n">
-        <v>480.8362723195767</v>
+        <v>493.1051092836722</v>
       </c>
       <c r="O10" t="n">
-        <v>21.92797921194693</v>
+        <v>22.20597012705529</v>
       </c>
       <c r="P10" t="n">
-        <v>420.5902773898257</v>
+        <v>421.0636222831874</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30913,28 +31013,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4623306132074742</v>
+        <v>0.4290014670838212</v>
       </c>
       <c r="J11" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K11" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03098413816772827</v>
+        <v>0.02643682544870107</v>
       </c>
       <c r="M11" t="n">
-        <v>15.11232258374058</v>
+        <v>15.20741108065699</v>
       </c>
       <c r="N11" t="n">
-        <v>367.7487356107347</v>
+        <v>374.4493290397851</v>
       </c>
       <c r="O11" t="n">
-        <v>19.17677594411361</v>
+        <v>19.3506932444237</v>
       </c>
       <c r="P11" t="n">
-        <v>413.1981825668963</v>
+        <v>413.552621464019</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30991,28 +31091,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4193860602577649</v>
+        <v>0.4072809413424933</v>
       </c>
       <c r="J12" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K12" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02729714794477789</v>
+        <v>0.02590290824637631</v>
       </c>
       <c r="M12" t="n">
-        <v>14.80121733750358</v>
+        <v>14.79756147133525</v>
       </c>
       <c r="N12" t="n">
-        <v>340.9480743071924</v>
+        <v>340.8260648615733</v>
       </c>
       <c r="O12" t="n">
-        <v>18.46477929213324</v>
+        <v>18.46147515399496</v>
       </c>
       <c r="P12" t="n">
-        <v>397.8551147357966</v>
+        <v>397.9845509212182</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31069,28 +31169,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3323868447702226</v>
+        <v>0.3390140907696207</v>
       </c>
       <c r="J13" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K13" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01837871091286114</v>
+        <v>0.01923351914755111</v>
       </c>
       <c r="M13" t="n">
-        <v>14.8069766738803</v>
+        <v>14.79020943505441</v>
       </c>
       <c r="N13" t="n">
-        <v>315.1715391329367</v>
+        <v>314.400220587507</v>
       </c>
       <c r="O13" t="n">
-        <v>17.75307125916349</v>
+        <v>17.73133442771601</v>
       </c>
       <c r="P13" t="n">
-        <v>390.7456765545676</v>
+        <v>390.673865283525</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31147,28 +31247,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1512727717076769</v>
+        <v>0.1756846593897206</v>
       </c>
       <c r="J14" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K14" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003564148955144897</v>
+        <v>0.004781889522947447</v>
       </c>
       <c r="M14" t="n">
-        <v>15.98966822387551</v>
+        <v>16.06968133323533</v>
       </c>
       <c r="N14" t="n">
-        <v>340.7615809228072</v>
+        <v>343.6699598624663</v>
       </c>
       <c r="O14" t="n">
-        <v>18.45972862538361</v>
+        <v>18.53833757008611</v>
       </c>
       <c r="P14" t="n">
-        <v>391.0537755261044</v>
+        <v>390.7890824125263</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31225,28 +31325,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3111336564729647</v>
+        <v>-0.2773352423482398</v>
       </c>
       <c r="J15" t="n">
+        <v>298</v>
+      </c>
+      <c r="K15" t="n">
         <v>297</v>
       </c>
-      <c r="K15" t="n">
-        <v>296</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.0120658053919126</v>
+        <v>0.009509631789921702</v>
       </c>
       <c r="M15" t="n">
-        <v>17.06436757950606</v>
+        <v>17.20477702901663</v>
       </c>
       <c r="N15" t="n">
-        <v>434.1875619935354</v>
+        <v>440.7782771474802</v>
       </c>
       <c r="O15" t="n">
-        <v>20.83716780163599</v>
+        <v>20.99472022074789</v>
       </c>
       <c r="P15" t="n">
-        <v>394.8306140523908</v>
+        <v>394.4718947254099</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31303,28 +31403,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3253873131681992</v>
+        <v>-0.2910710180338931</v>
       </c>
       <c r="J16" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K16" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01569216142400243</v>
+        <v>0.01241272268205562</v>
       </c>
       <c r="M16" t="n">
-        <v>14.73678662910473</v>
+        <v>14.88513612286565</v>
       </c>
       <c r="N16" t="n">
-        <v>363.0222166564312</v>
+        <v>370.0806971147644</v>
       </c>
       <c r="O16" t="n">
-        <v>19.053141910363</v>
+        <v>19.23748156892592</v>
       </c>
       <c r="P16" t="n">
-        <v>391.8563701120902</v>
+        <v>391.4911746660055</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31381,28 +31481,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4616275416245005</v>
+        <v>-0.4200725956534644</v>
       </c>
       <c r="J17" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K17" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03013122046253303</v>
+        <v>0.02448877160163454</v>
       </c>
       <c r="M17" t="n">
-        <v>14.96077722417131</v>
+        <v>15.13141405662672</v>
       </c>
       <c r="N17" t="n">
-        <v>375.9152053420282</v>
+        <v>386.9079720351159</v>
       </c>
       <c r="O17" t="n">
-        <v>19.38853283108416</v>
+        <v>19.66997641165632</v>
       </c>
       <c r="P17" t="n">
-        <v>394.1648908152559</v>
+        <v>393.7226323795211</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31459,28 +31559,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7326060796480643</v>
+        <v>-0.6858944754931926</v>
       </c>
       <c r="J18" t="n">
+        <v>298</v>
+      </c>
+      <c r="K18" t="n">
         <v>297</v>
       </c>
-      <c r="K18" t="n">
-        <v>296</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.05983541466789133</v>
+        <v>0.0515838509805211</v>
       </c>
       <c r="M18" t="n">
-        <v>16.88029180240541</v>
+        <v>17.04975858895362</v>
       </c>
       <c r="N18" t="n">
-        <v>463.1593528181</v>
+        <v>477.1255575939461</v>
       </c>
       <c r="O18" t="n">
-        <v>21.52113734954777</v>
+        <v>21.84320392236327</v>
       </c>
       <c r="P18" t="n">
-        <v>402.5568242555689</v>
+        <v>402.0610212712498</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31537,28 +31637,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5508936164388492</v>
+        <v>-0.5033195055474498</v>
       </c>
       <c r="J19" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K19" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04528258384030137</v>
+        <v>0.03674395593940294</v>
       </c>
       <c r="M19" t="n">
-        <v>14.09058161388116</v>
+        <v>14.26272181201326</v>
       </c>
       <c r="N19" t="n">
-        <v>350.2382863151467</v>
+        <v>365.1091715577783</v>
       </c>
       <c r="O19" t="n">
-        <v>18.71465431994796</v>
+        <v>19.1078301111816</v>
       </c>
       <c r="P19" t="n">
-        <v>399.83808242357</v>
+        <v>399.3323862032516</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31615,28 +31715,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4606903618296257</v>
+        <v>-0.4234721060447287</v>
       </c>
       <c r="J20" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K20" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03475924375118289</v>
+        <v>0.02889483533906279</v>
       </c>
       <c r="M20" t="n">
-        <v>14.3484591397654</v>
+        <v>14.48021018149711</v>
       </c>
       <c r="N20" t="n">
-        <v>322.6027603733837</v>
+        <v>331.3408991313293</v>
       </c>
       <c r="O20" t="n">
-        <v>17.9611458535747</v>
+        <v>18.20277174309806</v>
       </c>
       <c r="P20" t="n">
-        <v>392.6152692251697</v>
+        <v>392.2196521358618</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31693,28 +31793,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1898928571612616</v>
+        <v>-0.1528689262190008</v>
       </c>
       <c r="J21" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K21" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L21" t="n">
-        <v>0.006582579718174442</v>
+        <v>0.004172872557132057</v>
       </c>
       <c r="M21" t="n">
-        <v>14.10382017821298</v>
+        <v>14.23192651051554</v>
       </c>
       <c r="N21" t="n">
-        <v>297.8772914440252</v>
+        <v>306.596117170177</v>
       </c>
       <c r="O21" t="n">
-        <v>17.25912197778396</v>
+        <v>17.50988626948151</v>
       </c>
       <c r="P21" t="n">
-        <v>385.4806029961127</v>
+        <v>385.0870515121643</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31771,28 +31871,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0611463456958763</v>
+        <v>-0.0253879036578477</v>
       </c>
       <c r="J22" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K22" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.000537575885875996</v>
+        <v>9.124620417999552e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>16.27181832936999</v>
+        <v>16.4097158172907</v>
       </c>
       <c r="N22" t="n">
-        <v>380.3496358619474</v>
+        <v>388.1440899684554</v>
       </c>
       <c r="O22" t="n">
-        <v>19.50255459835833</v>
+        <v>19.70137279400741</v>
       </c>
       <c r="P22" t="n">
-        <v>378.045727999103</v>
+        <v>377.664528651128</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31849,28 +31949,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1812054919664189</v>
+        <v>0.2092172337145517</v>
       </c>
       <c r="J23" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K23" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004731988626041073</v>
+        <v>0.006254427918099381</v>
       </c>
       <c r="M23" t="n">
-        <v>16.25081812039547</v>
+        <v>16.36394064400132</v>
       </c>
       <c r="N23" t="n">
-        <v>378.2919887068296</v>
+        <v>382.5950577166978</v>
       </c>
       <c r="O23" t="n">
-        <v>19.44972978493093</v>
+        <v>19.56003726266128</v>
       </c>
       <c r="P23" t="n">
-        <v>371.4363325671624</v>
+        <v>371.1375391510047</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31927,28 +32027,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2895097213089846</v>
+        <v>0.3133785103464597</v>
       </c>
       <c r="J24" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K24" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01301386537841598</v>
+        <v>0.01515577600829976</v>
       </c>
       <c r="M24" t="n">
-        <v>15.60752190759772</v>
+        <v>15.66510262654034</v>
       </c>
       <c r="N24" t="n">
-        <v>349.3152519415615</v>
+        <v>352.2008356405116</v>
       </c>
       <c r="O24" t="n">
-        <v>18.68997731249456</v>
+        <v>18.76701456387008</v>
       </c>
       <c r="P24" t="n">
-        <v>366.8689380115968</v>
+        <v>366.6152620416947</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32005,28 +32105,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3625629319182518</v>
+        <v>0.3774376289564079</v>
       </c>
       <c r="J25" t="n">
+        <v>298</v>
+      </c>
+      <c r="K25" t="n">
         <v>297</v>
       </c>
-      <c r="K25" t="n">
-        <v>296</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02455964462325511</v>
+        <v>0.0266188933641166</v>
       </c>
       <c r="M25" t="n">
-        <v>14.34821379867639</v>
+        <v>14.36810912301995</v>
       </c>
       <c r="N25" t="n">
-        <v>286.5789563607117</v>
+        <v>287.1890565796784</v>
       </c>
       <c r="O25" t="n">
-        <v>16.928643074999</v>
+        <v>16.9466532560172</v>
       </c>
       <c r="P25" t="n">
-        <v>369.4054351059797</v>
+        <v>369.2474381099107</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32083,28 +32183,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3814961991729841</v>
+        <v>0.3918539803395258</v>
       </c>
       <c r="J26" t="n">
+        <v>298</v>
+      </c>
+      <c r="K26" t="n">
         <v>297</v>
       </c>
-      <c r="K26" t="n">
-        <v>296</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.02396546179473902</v>
+        <v>0.02538542124052678</v>
       </c>
       <c r="M26" t="n">
-        <v>15.00128870800196</v>
+        <v>14.98980620874587</v>
       </c>
       <c r="N26" t="n">
-        <v>324.6919386416501</v>
+        <v>324.3549723681512</v>
       </c>
       <c r="O26" t="n">
-        <v>18.01921026686936</v>
+        <v>18.00985764430555</v>
       </c>
       <c r="P26" t="n">
-        <v>365.5466622028079</v>
+        <v>365.436729935709</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32161,28 +32261,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2615062924585529</v>
+        <v>0.2784671771770872</v>
       </c>
       <c r="J27" t="n">
+        <v>298</v>
+      </c>
+      <c r="K27" t="n">
         <v>297</v>
       </c>
-      <c r="K27" t="n">
-        <v>296</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01182002481498945</v>
+        <v>0.01339897895749054</v>
       </c>
       <c r="M27" t="n">
-        <v>14.95222132452185</v>
+        <v>14.98443715949064</v>
       </c>
       <c r="N27" t="n">
-        <v>313.1797252852315</v>
+        <v>314.1531264289609</v>
       </c>
       <c r="O27" t="n">
-        <v>17.69688462089391</v>
+        <v>17.72436533219063</v>
       </c>
       <c r="P27" t="n">
-        <v>362.5412250137181</v>
+        <v>362.3612107346818</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32220,7 +32320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB298"/>
+  <dimension ref="A1:AB299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73831,6 +73931,148 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>-37.79778431185272,174.84151657381298</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>-37.79744365626257,174.8406380088038</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-37.797225631758984,174.8395775569997</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-37.79678945438413,174.838840643484</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-37.796238084708506,174.83826158536536</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-37.79557617805288,174.83784883946242</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-37.794851657108765,174.83754616235873</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-37.794069213061405,174.83727375024512</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-37.79332766937406,174.83708383619785</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-37.79267074341134,174.83671078916151</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-37.79201780574053,174.83629049896814</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-37.7913188921035,174.8359011733818</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-37.790596713767115,174.83559503223657</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-37.78988916806473,174.83546377451128</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-37.789170850965995,174.83543872537732</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-37.78846315359513,174.83528664104884</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-37.78777156834806,174.83514293212193</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>-37.78710109593414,174.83503768223736</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>-37.78639298015753,174.83514989075837</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>-37.785688370737226,174.83503606583815</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>-37.78497320709889,174.83498791551233</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>-37.78425163495721,174.8350102460048</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>-37.783537673353024,174.83499002062527</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>-37.7828350793992,174.83498393720615</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>-37.782132068890924,174.83493398035995</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>-37.78144029115757,174.83473100181138</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
